--- a/bills.xlsx
+++ b/bills.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -453,14 +458,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>1220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11-01-2025</t>
+          <t>12-10-2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5620</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12-20-2025</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
